--- a/data/GPS/Metricas_GPS (1).xlsx
+++ b/data/GPS/Metricas_GPS (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46451100-8101-4050-BCE8-5B50B7D92515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{46451100-8101-4050-BCE8-5B50B7D92515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0366BC04-80CD-48C2-BE3A-497287C4F414}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>eJy9lltv2jAUx7+KladNQhDSLoumahIb6staRlv1tosqYxvi4ksU26UF8d1nG9aFDLKSqXlKzsnxOb//8S2LAENNVPABLAIt/cM57EsQhVEcJuFh0ALBA2TOxVysDpbWM84lf2m4i88eNBpPXKHvi7VxR7GL4sZgOKdxMnNDkWTrIPu2jpiLGXXfMqhTZ/uS1tZPGSnaAnJvHxOUQucwgmrncMTFhCy0Wu13qu4mnn4MmSLWkRNskM+hpfYl4AST8WpYN467kfURYbj1eMyfBaxMqjbJUJHMDi9ycCqKnH2TQ0SlKOMdw7Orol4fX8iaMfhE8mKmgeSjnFRJ/nYefQ42Yal2tSvzDm0UWkftyoypud/azFFuVEqe2/TfvcVUVfR2yjdaS5WGAlEIbDG7GkvMX9LrZINZ5+Y1kOeCtA9rgn8E3QRMeSctw5/EJm0KPq4Jb+mjd60IbBXwlV+eNiXgfU0Brv9R0kq2KziT8LG5KUBCVyjYOAd+mDAcQXCR5VRoBd4c/ZmFt3+tI/Gp14QIiJDTEdXQ0UOEkdUhaYFK/N3zm0Y2MSa1+ftEwSoJlwN1u9/ZyVcLr8YctH8P3XE3dVRHFTX0UBucwkfKYZkaDQnek3p18dWipmIf6j7ZiZ2NDw4aabbK8D+a7fbjxkV75aHLxP3odvDqVyu9V20m8QtX9tD/I4ATCXGwdGkQo0ToVSlhGPPO531AZuBa5tORlNNg+QslaRAI</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jorge_vicaria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro_Garcia_Gumiel </t>
   </si>
   <si>
     <t xml:space="preserve">Javier_Caamano_Olmedo </t>
@@ -437,7 +434,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="22.21875" customWidth="1"/>
@@ -783,40 +780,40 @@
         <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2">
-        <v>4.202</v>
+        <v>4.8220000000000001</v>
       </c>
       <c r="F8" s="2">
-        <v>0.20399999999999999</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K8" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L8" s="2">
-        <v>4.3150000000000004</v>
+        <v>4.7969999999999997</v>
       </c>
       <c r="M8" s="2">
-        <v>-5.375</v>
+        <v>-5.0250000000000004</v>
       </c>
       <c r="N8" s="2">
-        <v>24.966000000000001</v>
+        <v>26.82</v>
       </c>
       <c r="O8" s="2">
-        <v>873.8</v>
+        <v>983.6</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -830,40 +827,40 @@
         <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2">
-        <v>4.8220000000000001</v>
+        <v>4.6130000000000004</v>
       </c>
       <c r="F9" s="2">
-        <v>0.51900000000000002</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="G9" s="2">
-        <v>8.9999999999999993E-3</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="H9" s="2">
-        <v>0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I9" s="2">
         <v>3</v>
       </c>
       <c r="J9" s="2">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K9" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L9" s="2">
-        <v>4.7969999999999997</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="M9" s="2">
-        <v>-5.0250000000000004</v>
+        <v>-5.7569999999999997</v>
       </c>
       <c r="N9" s="2">
-        <v>26.82</v>
+        <v>29.257000000000001</v>
       </c>
       <c r="O9" s="2">
-        <v>983.6</v>
+        <v>1136.7</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -880,37 +877,37 @@
         <v>25</v>
       </c>
       <c r="E10" s="2">
-        <v>4.6130000000000004</v>
+        <v>2.6</v>
       </c>
       <c r="F10" s="2">
-        <v>0.66100000000000003</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="G10" s="2">
-        <v>7.3999999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K10" s="2">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="L10" s="2">
-        <v>4.9800000000000004</v>
+        <v>4.4889999999999999</v>
       </c>
       <c r="M10" s="2">
-        <v>-5.7569999999999997</v>
+        <v>-5.5880000000000001</v>
       </c>
       <c r="N10" s="2">
-        <v>29.257000000000001</v>
+        <v>24.538</v>
       </c>
       <c r="O10" s="2">
-        <v>1136.7</v>
+        <v>420.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -924,40 +921,40 @@
         <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2">
-        <v>2.6</v>
+        <v>4.8259999999999996</v>
       </c>
       <c r="F11" s="2">
-        <v>0.34799999999999998</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K11" s="2">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="L11" s="2">
-        <v>4.4889999999999999</v>
+        <v>4.7859999999999996</v>
       </c>
       <c r="M11" s="2">
-        <v>-5.5880000000000001</v>
+        <v>-6.016</v>
       </c>
       <c r="N11" s="2">
-        <v>24.538</v>
+        <v>26.251000000000001</v>
       </c>
       <c r="O11" s="2">
-        <v>420.9</v>
+        <v>1117.5999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -971,40 +968,40 @@
         <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2">
-        <v>4.8259999999999996</v>
+        <v>2.1659999999999999</v>
       </c>
       <c r="F12" s="2">
-        <v>0.64900000000000002</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="G12" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K12" s="2">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L12" s="2">
-        <v>4.7859999999999996</v>
+        <v>4.6349999999999998</v>
       </c>
       <c r="M12" s="2">
-        <v>-6.016</v>
+        <v>-4.7480000000000002</v>
       </c>
       <c r="N12" s="2">
-        <v>26.251000000000001</v>
+        <v>22.774000000000001</v>
       </c>
       <c r="O12" s="2">
-        <v>1117.5999999999999</v>
+        <v>521.6</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1015,89 +1012,42 @@
         <v>65.09</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E13" s="2">
-        <v>2.1659999999999999</v>
+        <v>3.843</v>
       </c>
       <c r="F13" s="2">
-        <v>9.2999999999999999E-2</v>
+        <v>0.64</v>
       </c>
       <c r="G13" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H13" s="2">
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K13" s="2">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="L13" s="2">
-        <v>4.6349999999999998</v>
+        <v>4.8920000000000003</v>
       </c>
       <c r="M13" s="2">
-        <v>-4.7480000000000002</v>
+        <v>-5.1630000000000003</v>
       </c>
       <c r="N13" s="2">
-        <v>22.774000000000001</v>
+        <v>25.603000000000002</v>
       </c>
       <c r="O13" s="2">
-        <v>521.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>46238</v>
-      </c>
-      <c r="B14" s="2">
-        <v>65.09</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="2">
-        <v>3.843</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.64</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>33</v>
-      </c>
-      <c r="K14" s="2">
-        <v>37</v>
-      </c>
-      <c r="L14" s="2">
-        <v>4.8920000000000003</v>
-      </c>
-      <c r="M14" s="2">
-        <v>-5.1630000000000003</v>
-      </c>
-      <c r="N14" s="2">
-        <v>25.603000000000002</v>
-      </c>
-      <c r="O14" s="2">
         <v>698.3</v>
       </c>
     </row>
